--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/110.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/110.xlsx
@@ -426,13 +426,13 @@
         <v>4.926903921445764</v>
       </c>
       <c r="E2">
-        <v>-16.50385804412394</v>
+        <v>-15.76501486740248</v>
       </c>
       <c r="F2">
-        <v>-3.117179818678159</v>
+        <v>-2.303651789532404</v>
       </c>
       <c r="G2">
-        <v>-10.55534123753505</v>
+        <v>-11.42193281171345</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>4.768710491141849</v>
       </c>
       <c r="E3">
-        <v>-17.08583035274568</v>
+        <v>-17.61269113269408</v>
       </c>
       <c r="F3">
-        <v>-2.963950901610515</v>
+        <v>-2.38451038845447</v>
       </c>
       <c r="G3">
-        <v>-10.26440387445282</v>
+        <v>-10.25171124285525</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>4.572112663826137</v>
       </c>
       <c r="E4">
-        <v>-17.10835498245984</v>
+        <v>-16.82254487393973</v>
       </c>
       <c r="F4">
-        <v>-3.581193132825914</v>
+        <v>-2.28969297042783</v>
       </c>
       <c r="G4">
-        <v>-10.26530765338504</v>
+        <v>-10.39882195498384</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>4.368369200532107</v>
       </c>
       <c r="E5">
-        <v>-18.33469291458102</v>
+        <v>-17.17140945454264</v>
       </c>
       <c r="F5">
-        <v>-3.138491226849982</v>
+        <v>-2.171068273244732</v>
       </c>
       <c r="G5">
-        <v>-10.55093159087674</v>
+        <v>-10.2707336375239</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>4.179720113577331</v>
       </c>
       <c r="E6">
-        <v>-18.49783119070734</v>
+        <v>-17.97107003718711</v>
       </c>
       <c r="F6">
-        <v>-3.007835321508625</v>
+        <v>-2.19376305497923</v>
       </c>
       <c r="G6">
-        <v>-10.85521376302777</v>
+        <v>-9.80220205898747</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>4.036679161036381</v>
       </c>
       <c r="E7">
-        <v>-19.45526380777904</v>
+        <v>-17.75666037834594</v>
       </c>
       <c r="F7">
-        <v>-2.925522109427243</v>
+        <v>-2.491674622619836</v>
       </c>
       <c r="G7">
-        <v>-10.05291960431309</v>
+        <v>-9.606800419077528</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>3.966227399621735</v>
       </c>
       <c r="E8">
-        <v>-18.96949892945025</v>
+        <v>-18.92851623968084</v>
       </c>
       <c r="F8">
-        <v>-2.79357146583531</v>
+        <v>-2.528733295118877</v>
       </c>
       <c r="G8">
-        <v>-10.02165150169468</v>
+        <v>-9.850218211489059</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>3.99242778609137</v>
       </c>
       <c r="E9">
-        <v>-20.18724634637888</v>
+        <v>-18.09679858953607</v>
       </c>
       <c r="F9">
-        <v>-2.814732111139823</v>
+        <v>-2.59511865877923</v>
       </c>
       <c r="G9">
-        <v>-9.86811171012882</v>
+        <v>-9.29677445041586</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>4.132420192607112</v>
       </c>
       <c r="E10">
-        <v>-20.71972243409679</v>
+        <v>-20.76107645873484</v>
       </c>
       <c r="F10">
-        <v>-2.930689465285907</v>
+        <v>-2.767044656495461</v>
       </c>
       <c r="G10">
-        <v>-9.659494372426106</v>
+        <v>-9.121785634301062</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>4.393057173053096</v>
       </c>
       <c r="E11">
-        <v>-21.34889049882648</v>
+        <v>-21.94104734549148</v>
       </c>
       <c r="F11">
-        <v>-2.730324786264165</v>
+        <v>-2.241482815952301</v>
       </c>
       <c r="G11">
-        <v>-9.126185349322755</v>
+        <v>-8.110473561873423</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>4.765684149430306</v>
       </c>
       <c r="E12">
-        <v>-22.3412240650753</v>
+        <v>-21.91895292080806</v>
       </c>
       <c r="F12">
-        <v>-2.6106149277834</v>
+        <v>-2.047579402672396</v>
       </c>
       <c r="G12">
-        <v>-8.887031539565804</v>
+        <v>-7.874391938376916</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>5.231358573061298</v>
       </c>
       <c r="E13">
-        <v>-21.66941136061538</v>
+        <v>-22.61100337560826</v>
       </c>
       <c r="F13">
-        <v>-2.552925765117637</v>
+        <v>-2.720959264408114</v>
       </c>
       <c r="G13">
-        <v>-8.852055625943404</v>
+        <v>-6.283062355832345</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>5.760804877901093</v>
       </c>
       <c r="E14">
-        <v>-23.38955674090298</v>
+        <v>-23.15998122261012</v>
       </c>
       <c r="F14">
-        <v>-2.611808605210834</v>
+        <v>-2.735567523556483</v>
       </c>
       <c r="G14">
-        <v>-7.687402394682261</v>
+        <v>-6.952951245703869</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>6.314348176336729</v>
       </c>
       <c r="E15">
-        <v>-24.24886185470247</v>
+        <v>-24.86151004625218</v>
       </c>
       <c r="F15">
-        <v>-2.422588781226357</v>
+        <v>-2.319255746298938</v>
       </c>
       <c r="G15">
-        <v>-7.312006393802144</v>
+        <v>-6.393399528110714</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>6.853130521029737</v>
       </c>
       <c r="E16">
-        <v>-24.79317084500243</v>
+        <v>-24.06228419711244</v>
       </c>
       <c r="F16">
-        <v>-2.321628190540556</v>
+        <v>-2.203122778263462</v>
       </c>
       <c r="G16">
-        <v>-6.991611796511479</v>
+        <v>-5.579233753092212</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>7.340991945459446</v>
       </c>
       <c r="E17">
-        <v>-25.40628094090092</v>
+        <v>-25.40256759221463</v>
       </c>
       <c r="F17">
-        <v>-1.926086897540806</v>
+        <v>-2.154071002506689</v>
       </c>
       <c r="G17">
-        <v>-6.113171779848027</v>
+        <v>-5.405790961744255</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>7.744724030590691</v>
       </c>
       <c r="E18">
-        <v>-25.88966837037568</v>
+        <v>-26.70325401059374</v>
       </c>
       <c r="F18">
-        <v>-2.134833826311476</v>
+        <v>-2.248333414373453</v>
       </c>
       <c r="G18">
-        <v>-5.682728027740908</v>
+        <v>-4.363075054331088</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>8.043010794649213</v>
       </c>
       <c r="E19">
-        <v>-27.05970378515949</v>
+        <v>-27.22228958745688</v>
       </c>
       <c r="F19">
-        <v>-1.705779273296667</v>
+        <v>-1.89080507312077</v>
       </c>
       <c r="G19">
-        <v>-5.762260573776359</v>
+        <v>-3.733247076030284</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>8.22499655451756</v>
       </c>
       <c r="E20">
-        <v>-28.06001199413582</v>
+        <v>-27.5194435233662</v>
       </c>
       <c r="F20">
-        <v>-1.646106999068601</v>
+        <v>-1.332862350802177</v>
       </c>
       <c r="G20">
-        <v>-5.117015384899169</v>
+        <v>-3.351948372453646</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>8.286434016081127</v>
       </c>
       <c r="E21">
-        <v>-28.54241221627692</v>
+        <v>-27.63674458558689</v>
       </c>
       <c r="F21">
-        <v>-1.537991799124821</v>
+        <v>-1.372032531810954</v>
       </c>
       <c r="G21">
-        <v>-5.283449751340489</v>
+        <v>-3.49492752374923</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>8.234107695687996</v>
       </c>
       <c r="E22">
-        <v>-29.05653892731575</v>
+        <v>-28.863634991537</v>
       </c>
       <c r="F22">
-        <v>-1.648331993912521</v>
+        <v>-1.558426794584482</v>
       </c>
       <c r="G22">
-        <v>-4.549011844544254</v>
+        <v>-3.07421346498203</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>8.082936630603857</v>
       </c>
       <c r="E23">
-        <v>-29.67403485029066</v>
+        <v>-28.97355011265118</v>
       </c>
       <c r="F23">
-        <v>-1.494135543718407</v>
+        <v>-1.283973763423755</v>
       </c>
       <c r="G23">
-        <v>-4.744022840080563</v>
+        <v>-2.626160921151528</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.848169338083306</v>
       </c>
       <c r="E24">
-        <v>-30.20952690169768</v>
+        <v>-30.32050394996666</v>
       </c>
       <c r="F24">
-        <v>-1.509944107233433</v>
+        <v>-1.16295591281397</v>
       </c>
       <c r="G24">
-        <v>-4.477838425995463</v>
+        <v>-3.327016653997395</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.547963060815977</v>
       </c>
       <c r="E25">
-        <v>-29.93448324013081</v>
+        <v>-31.48141901809902</v>
       </c>
       <c r="F25">
-        <v>-1.326300024237199</v>
+        <v>-1.042361357947015</v>
       </c>
       <c r="G25">
-        <v>-4.569431289430478</v>
+        <v>-3.342884098767122</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>7.204723538414143</v>
       </c>
       <c r="E26">
-        <v>-30.90884329304319</v>
+        <v>-31.39891927862728</v>
       </c>
       <c r="F26">
-        <v>-1.273560356803163</v>
+        <v>-1.218850003317867</v>
       </c>
       <c r="G26">
-        <v>-4.092222771035616</v>
+        <v>-1.964770201679312</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>6.835228634224188</v>
       </c>
       <c r="E27">
-        <v>-31.35706259337439</v>
+        <v>-30.01348473343162</v>
       </c>
       <c r="F27">
-        <v>-1.033842427576625</v>
+        <v>-1.157616256535524</v>
       </c>
       <c r="G27">
-        <v>-4.436390395843787</v>
+        <v>-3.099880124547999</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.45403698568201</v>
       </c>
       <c r="E28">
-        <v>-30.97474843951382</v>
+        <v>-31.17088117726003</v>
       </c>
       <c r="F28">
-        <v>-1.136952631672691</v>
+        <v>-0.7190777251260634</v>
       </c>
       <c r="G28">
-        <v>-4.13785864129447</v>
+        <v>-2.40284807179999</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.07813903344663</v>
       </c>
       <c r="E29">
-        <v>-30.92343630053291</v>
+        <v>-30.64583857962571</v>
       </c>
       <c r="F29">
-        <v>-1.180343344598732</v>
+        <v>-1.101784293586838</v>
       </c>
       <c r="G29">
-        <v>-4.732293577234925</v>
+        <v>-4.684678000743587</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.716028451917732</v>
       </c>
       <c r="E30">
-        <v>-30.79611372533325</v>
+        <v>-31.14083475221914</v>
       </c>
       <c r="F30">
-        <v>-1.176842663954501</v>
+        <v>-1.193681716518609</v>
       </c>
       <c r="G30">
-        <v>-4.846348492153896</v>
+        <v>-3.55329575215212</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.370793812163734</v>
       </c>
       <c r="E31">
-        <v>-29.9929820673619</v>
+        <v>-31.32626444164822</v>
       </c>
       <c r="F31">
-        <v>-0.9807283380765236</v>
+        <v>-0.9233837762503251</v>
       </c>
       <c r="G31">
-        <v>-5.187215503059415</v>
+        <v>-3.475209914517331</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.048574278221181</v>
       </c>
       <c r="E32">
-        <v>-29.17483625381812</v>
+        <v>-32.15082257438686</v>
       </c>
       <c r="F32">
-        <v>-1.094092073884442</v>
+        <v>-0.7066472438796541</v>
       </c>
       <c r="G32">
-        <v>-5.130538963427091</v>
+        <v>-4.188423913861297</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.748392661590478</v>
       </c>
       <c r="E33">
-        <v>-30.48358109169388</v>
+        <v>-30.50212066428128</v>
       </c>
       <c r="F33">
-        <v>-1.015099786720884</v>
+        <v>-0.9660372421878745</v>
       </c>
       <c r="G33">
-        <v>-5.273961727824937</v>
+        <v>-3.905514623711799</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.465055474665371</v>
       </c>
       <c r="E34">
-        <v>-29.34516574666862</v>
+        <v>-29.34053764623278</v>
       </c>
       <c r="F34">
-        <v>-1.014541467091397</v>
+        <v>-0.75622668967201</v>
       </c>
       <c r="G34">
-        <v>-4.98078312541262</v>
+        <v>-3.868112080209114</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.197989805620623</v>
       </c>
       <c r="E35">
-        <v>-29.23145123586201</v>
+        <v>-30.3021704229466</v>
       </c>
       <c r="F35">
-        <v>-0.871991034213241</v>
+        <v>-0.8092935622301519</v>
       </c>
       <c r="G35">
-        <v>-5.497976412830801</v>
+        <v>-3.920537879369012</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>3.943254782618622</v>
       </c>
       <c r="E36">
-        <v>-29.68913504686924</v>
+        <v>-28.68926609987166</v>
       </c>
       <c r="F36">
-        <v>-0.8611054581730526</v>
+        <v>-0.6844271166669601</v>
       </c>
       <c r="G36">
-        <v>-5.642567799804009</v>
+        <v>-4.353931327551621</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.694518068901795</v>
       </c>
       <c r="E37">
-        <v>-28.11122450668856</v>
+        <v>-29.56810025782923</v>
       </c>
       <c r="F37">
-        <v>-0.9438593617127232</v>
+        <v>-0.8777879492980318</v>
       </c>
       <c r="G37">
-        <v>-5.492864930518166</v>
+        <v>-4.021095700124374</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.450905947892337</v>
       </c>
       <c r="E38">
-        <v>-28.85369046261616</v>
+        <v>-28.64289452603311</v>
       </c>
       <c r="F38">
-        <v>-0.7234846397089567</v>
+        <v>-0.569952540171888</v>
       </c>
       <c r="G38">
-        <v>-5.889560981397953</v>
+        <v>-3.479987031730499</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.211071314322846</v>
       </c>
       <c r="E39">
-        <v>-27.71797635233648</v>
+        <v>-27.10430019718703</v>
       </c>
       <c r="F39">
-        <v>-0.9007726596235097</v>
+        <v>-0.5824890524458557</v>
       </c>
       <c r="G39">
-        <v>-5.852903310641604</v>
+        <v>-4.097794419178209</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.971999403890013</v>
       </c>
       <c r="E40">
-        <v>-26.96154005409522</v>
+        <v>-27.23544480444916</v>
       </c>
       <c r="F40">
-        <v>-1.046702831505087</v>
+        <v>-0.6959762149967907</v>
       </c>
       <c r="G40">
-        <v>-5.337530823270023</v>
+        <v>-3.66017671488749</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.735267963103382</v>
       </c>
       <c r="E41">
-        <v>-27.58227157174862</v>
+        <v>-26.56494082897746</v>
       </c>
       <c r="F41">
-        <v>-0.57064257021842</v>
+        <v>-1.009025368556155</v>
       </c>
       <c r="G41">
-        <v>-5.765567808770091</v>
+        <v>-4.345999260439527</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.503127776913538</v>
       </c>
       <c r="E42">
-        <v>-25.53435071431184</v>
+        <v>-26.48657558627472</v>
       </c>
       <c r="F42">
-        <v>-0.5957860059955934</v>
+        <v>-0.6969661140431362</v>
       </c>
       <c r="G42">
-        <v>-5.697403676116497</v>
+        <v>-4.153878371159003</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>2.275560072710549</v>
       </c>
       <c r="E43">
-        <v>-25.39012787411556</v>
+        <v>-25.67452057027126</v>
       </c>
       <c r="F43">
-        <v>-0.4380897035246515</v>
+        <v>-0.4766808557188721</v>
       </c>
       <c r="G43">
-        <v>-5.388698615124998</v>
+        <v>-4.837343808287078</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>2.05485300442598</v>
       </c>
       <c r="E44">
-        <v>-25.26849306226953</v>
+        <v>-24.93410601306914</v>
       </c>
       <c r="F44">
-        <v>-0.6300274009577137</v>
+        <v>-0.3298436215312289</v>
       </c>
       <c r="G44">
-        <v>-6.408796875413865</v>
+        <v>-4.087813124377306</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.843851731347511</v>
       </c>
       <c r="E45">
-        <v>-24.33765164457087</v>
+        <v>-23.73313206386493</v>
       </c>
       <c r="F45">
-        <v>-0.6575482511809218</v>
+        <v>-0.3014471869632618</v>
       </c>
       <c r="G45">
-        <v>-6.017983663957362</v>
+        <v>-4.620380585279863</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.640778603673818</v>
       </c>
       <c r="E46">
-        <v>-24.09161059478612</v>
+        <v>-23.86032784179237</v>
       </c>
       <c r="F46">
-        <v>-0.4764282036610182</v>
+        <v>-0.172911902173071</v>
       </c>
       <c r="G46">
-        <v>-7.069038835583953</v>
+        <v>-4.231076982589268</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.44447310461919</v>
       </c>
       <c r="E47">
-        <v>-22.65706701321428</v>
+        <v>-23.09805886902923</v>
       </c>
       <c r="F47">
-        <v>-0.5469719716834242</v>
+        <v>-0.1994022633471964</v>
       </c>
       <c r="G47">
-        <v>-6.284863292605708</v>
+        <v>-4.742652274227305</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.25464621407484</v>
       </c>
       <c r="E48">
-        <v>-22.77970714629001</v>
+        <v>-22.08178778917587</v>
       </c>
       <c r="F48">
-        <v>-0.4016705306605712</v>
+        <v>-0.1433201334428642</v>
       </c>
       <c r="G48">
-        <v>-6.636780904521314</v>
+        <v>-5.34313226632247</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.0664468162929</v>
       </c>
       <c r="E49">
-        <v>-21.38180344791423</v>
+        <v>-22.72938674311678</v>
       </c>
       <c r="F49">
-        <v>-0.4597200331465522</v>
+        <v>-0.2563326414719952</v>
       </c>
       <c r="G49">
-        <v>-6.500876389043153</v>
+        <v>-3.823360125609246</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.8760032902628042</v>
       </c>
       <c r="E50">
-        <v>-21.39355483796414</v>
+        <v>-22.04518413377187</v>
       </c>
       <c r="F50">
-        <v>-0.3316867390024578</v>
+        <v>-0.6355327307167192</v>
       </c>
       <c r="G50">
-        <v>-6.459931561813447</v>
+        <v>-4.765488417357197</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.6827536199869884</v>
       </c>
       <c r="E51">
-        <v>-20.18674821423804</v>
+        <v>-21.08601258268122</v>
       </c>
       <c r="F51">
-        <v>-0.1026009053908517</v>
+        <v>-0.4289296167844945</v>
       </c>
       <c r="G51">
-        <v>-6.513036022808897</v>
+        <v>-4.503256794645987</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>0.4839932198875618</v>
       </c>
       <c r="E52">
-        <v>-20.35267603035309</v>
+        <v>-20.26827433179813</v>
       </c>
       <c r="F52">
-        <v>-0.435806722962536</v>
+        <v>0.08245471565975224</v>
       </c>
       <c r="G52">
-        <v>-6.50039304939442</v>
+        <v>-5.747346566121943</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>0.2793134321047563</v>
       </c>
       <c r="E53">
-        <v>-19.72543709555067</v>
+        <v>-18.93651352477838</v>
       </c>
       <c r="F53">
-        <v>-0.4477045639689454</v>
+        <v>-0.4130133655071049</v>
       </c>
       <c r="G53">
-        <v>-6.449797981917738</v>
+        <v>-3.992005936470798</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>0.07300943723200326</v>
       </c>
       <c r="E54">
-        <v>-19.58285356294516</v>
+        <v>-19.67885721190777</v>
       </c>
       <c r="F54">
-        <v>-0.08948536430232715</v>
+        <v>-0.005435894144678108</v>
       </c>
       <c r="G54">
-        <v>-7.06364595690048</v>
+        <v>-5.500171304523337</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.1318979041630178</v>
       </c>
       <c r="E55">
-        <v>-18.36023803645828</v>
+        <v>-18.63210044503477</v>
       </c>
       <c r="F55">
-        <v>-0.4445493125316821</v>
+        <v>-0.1801336091906771</v>
       </c>
       <c r="G55">
-        <v>-6.673127383996973</v>
+        <v>-5.508179514182834</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.330825378171748</v>
       </c>
       <c r="E56">
-        <v>-17.23204572150534</v>
+        <v>-19.05901327515987</v>
       </c>
       <c r="F56">
-        <v>-0.4999554946353298</v>
+        <v>-0.4919418683806474</v>
       </c>
       <c r="G56">
-        <v>-7.180048048606794</v>
+        <v>-6.297155348193022</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.5158371508336338</v>
       </c>
       <c r="E57">
-        <v>-17.43253937972094</v>
+        <v>-17.11698625391845</v>
       </c>
       <c r="F57">
-        <v>-0.3404293285716038</v>
+        <v>-0.1841553329312687</v>
       </c>
       <c r="G57">
-        <v>-6.85297277041788</v>
+        <v>-5.909629508457016</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-0.6810806456178579</v>
       </c>
       <c r="E58">
-        <v>-16.41977333874951</v>
+        <v>-16.92967045506518</v>
       </c>
       <c r="F58">
-        <v>-0.5068905865315673</v>
+        <v>-0.2000624721672276</v>
       </c>
       <c r="G58">
-        <v>-6.868032442076024</v>
+        <v>-5.289590813315836</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.8209261972392092</v>
       </c>
       <c r="E59">
-        <v>-16.68934433947812</v>
+        <v>-16.82838207693562</v>
       </c>
       <c r="F59">
-        <v>-0.4408448535063627</v>
+        <v>-0.08072372228291677</v>
       </c>
       <c r="G59">
-        <v>-7.23089802809</v>
+        <v>-6.153192964872275</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.9287328537779269</v>
       </c>
       <c r="E60">
-        <v>-16.82008138407956</v>
+        <v>-15.33365507580184</v>
       </c>
       <c r="F60">
-        <v>-0.3157961671145549</v>
+        <v>-0.5862813184158718</v>
       </c>
       <c r="G60">
-        <v>-7.557900474277051</v>
+        <v>-6.422161547755902</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.000420334048562</v>
       </c>
       <c r="E61">
-        <v>-15.5533132360179</v>
+        <v>-16.09472853142695</v>
       </c>
       <c r="F61">
-        <v>-0.6938771319980969</v>
+        <v>-0.7498109841373278</v>
       </c>
       <c r="G61">
-        <v>-7.259719637554895</v>
+        <v>-6.631891228759811</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.033287863268161</v>
       </c>
       <c r="E62">
-        <v>-14.54331862113916</v>
+        <v>-15.17766726013363</v>
       </c>
       <c r="F62">
-        <v>-0.893442436476137</v>
+        <v>-0.5655075206884659</v>
       </c>
       <c r="G62">
-        <v>-6.770341553757671</v>
+        <v>-6.524166076911926</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.025555810648248</v>
       </c>
       <c r="E63">
-        <v>-14.85094238895422</v>
+        <v>-14.28465218582103</v>
       </c>
       <c r="F63">
-        <v>-0.6999946252677712</v>
+        <v>-1.014760156085736</v>
       </c>
       <c r="G63">
-        <v>-7.634648851513974</v>
+        <v>-7.086253672388163</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.9778335239626168</v>
       </c>
       <c r="E64">
-        <v>-14.78603577100228</v>
+        <v>-13.73717326371571</v>
       </c>
       <c r="F64">
-        <v>-1.145888230846689</v>
+        <v>-1.261662515796754</v>
       </c>
       <c r="G64">
-        <v>-7.853482532750879</v>
+        <v>-6.253734232899942</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.8916999571705064</v>
       </c>
       <c r="E65">
-        <v>-13.50075974967127</v>
+        <v>-13.79722082905742</v>
       </c>
       <c r="F65">
-        <v>-1.202440873435811</v>
+        <v>-0.9167121051881778</v>
       </c>
       <c r="G65">
-        <v>-7.807767209399083</v>
+        <v>-6.273263141036102</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.7708555727521911</v>
       </c>
       <c r="E66">
-        <v>-14.4639933419468</v>
+        <v>-14.49019056408117</v>
       </c>
       <c r="F66">
-        <v>-1.302093471992592</v>
+        <v>-0.8535863672578415</v>
       </c>
       <c r="G66">
-        <v>-7.948425668271637</v>
+        <v>-6.952894966429702</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.6199505161347489</v>
       </c>
       <c r="E67">
-        <v>-14.50273443708242</v>
+        <v>-13.27580780334024</v>
       </c>
       <c r="F67">
-        <v>-1.408590042031302</v>
+        <v>-1.325850220737479</v>
       </c>
       <c r="G67">
-        <v>-7.824895972019272</v>
+        <v>-7.799259107363156</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-0.4429432829299358</v>
       </c>
       <c r="E68">
-        <v>-14.02199163642813</v>
+        <v>-13.7030466835939</v>
       </c>
       <c r="F68">
-        <v>-1.520632531831755</v>
+        <v>-1.50306368758578</v>
       </c>
       <c r="G68">
-        <v>-7.611554485832019</v>
+        <v>-6.7312373898478</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.2459786252629282</v>
       </c>
       <c r="E69">
-        <v>-13.58800532990305</v>
+        <v>-13.40930268861236</v>
       </c>
       <c r="F69">
-        <v>-1.498438084008547</v>
+        <v>-1.425521871744524</v>
       </c>
       <c r="G69">
-        <v>-7.359376989923575</v>
+        <v>-5.521643502891051</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.03493565739153409</v>
       </c>
       <c r="E70">
-        <v>-14.75944457162924</v>
+        <v>-14.00113348514881</v>
       </c>
       <c r="F70">
-        <v>-1.840200936851151</v>
+        <v>-1.732151177932192</v>
       </c>
       <c r="G70">
-        <v>-8.144353684922324</v>
+        <v>-6.345323785789418</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.1864398100847792</v>
       </c>
       <c r="E71">
-        <v>-13.66239457242705</v>
+        <v>-12.33892087284134</v>
       </c>
       <c r="F71">
-        <v>-1.833382644758708</v>
+        <v>-1.705929207796573</v>
       </c>
       <c r="G71">
-        <v>-7.287342829534573</v>
+        <v>-7.380968367930702</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.4122083394043556</v>
       </c>
       <c r="E72">
-        <v>-13.43927665806913</v>
+        <v>-12.02807283153282</v>
       </c>
       <c r="F72">
-        <v>-1.959895056351262</v>
+        <v>-1.581232577550955</v>
       </c>
       <c r="G72">
-        <v>-7.404708289992816</v>
+        <v>-6.771116221413861</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.636869521391526</v>
       </c>
       <c r="E73">
-        <v>-13.13333295411092</v>
+        <v>-12.44993188466537</v>
       </c>
       <c r="F73">
-        <v>-2.144249050211695</v>
+        <v>-1.618213383514133</v>
       </c>
       <c r="G73">
-        <v>-7.151775989701418</v>
+        <v>-6.618099496043206</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.85713929368414</v>
       </c>
       <c r="E74">
-        <v>-13.5284694821242</v>
+        <v>-14.0768767414011</v>
       </c>
       <c r="F74">
-        <v>-2.333921162798101</v>
+        <v>-1.908717689838906</v>
       </c>
       <c r="G74">
-        <v>-6.754543630444269</v>
+        <v>-5.76112174611085</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>1.066940759878766</v>
       </c>
       <c r="E75">
-        <v>-14.0348434456619</v>
+        <v>-12.99353443302013</v>
       </c>
       <c r="F75">
-        <v>-2.347390416767621</v>
+        <v>-2.180060201402121</v>
       </c>
       <c r="G75">
-        <v>-6.871776669080941</v>
+        <v>-4.908646338111901</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>1.260692219103361</v>
       </c>
       <c r="E76">
-        <v>-14.70524779470544</v>
+        <v>-13.95941718259015</v>
       </c>
       <c r="F76">
-        <v>-2.481058265985558</v>
+        <v>-2.32748806154796</v>
       </c>
       <c r="G76">
-        <v>-6.64529562764832</v>
+        <v>-5.186275308126262</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>1.435348441590536</v>
       </c>
       <c r="E77">
-        <v>-14.8104306604816</v>
+        <v>-13.1473712235347</v>
       </c>
       <c r="F77">
-        <v>-2.111506171881239</v>
+        <v>-2.143085194010762</v>
       </c>
       <c r="G77">
-        <v>-6.216298583941863</v>
+        <v>-6.435357382275438</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.586735328699619</v>
       </c>
       <c r="E78">
-        <v>-14.01816054741765</v>
+        <v>-14.13534386931413</v>
       </c>
       <c r="F78">
-        <v>-2.515301317682483</v>
+        <v>-2.195832316751423</v>
       </c>
       <c r="G78">
-        <v>-5.872700372966445</v>
+        <v>-5.429746069266422</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.711394858154515</v>
       </c>
       <c r="E79">
-        <v>-15.06253080848861</v>
+        <v>-15.08295875473721</v>
       </c>
       <c r="F79">
-        <v>-2.523435885577975</v>
+        <v>-2.181046786978855</v>
       </c>
       <c r="G79">
-        <v>-6.322345289201337</v>
+        <v>-4.75993663248784</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.808487235225176</v>
       </c>
       <c r="E80">
-        <v>-15.63013426908402</v>
+        <v>-15.69852781202186</v>
       </c>
       <c r="F80">
-        <v>-2.629852932346016</v>
+        <v>-2.505225884962233</v>
       </c>
       <c r="G80">
-        <v>-6.040538410716416</v>
+        <v>-4.634937054016038</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.876588885674913</v>
       </c>
       <c r="E81">
-        <v>-16.74547024632918</v>
+        <v>-15.57884477247314</v>
       </c>
       <c r="F81">
-        <v>-2.572974741367593</v>
+        <v>-2.121656986035144</v>
       </c>
       <c r="G81">
-        <v>-5.519014929732869</v>
+        <v>-5.253019216743508</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.914417766994742</v>
       </c>
       <c r="E82">
-        <v>-16.87802773748171</v>
+        <v>-16.14613576836202</v>
       </c>
       <c r="F82">
-        <v>-2.51888069322998</v>
+        <v>-2.175739437029118</v>
       </c>
       <c r="G82">
-        <v>-5.823171301153409</v>
+        <v>-5.381676948036204</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.921944914738992</v>
       </c>
       <c r="E83">
-        <v>-17.93149117436007</v>
+        <v>-18.15549214114948</v>
       </c>
       <c r="F83">
-        <v>-2.784831361368373</v>
+        <v>-2.41027427141634</v>
       </c>
       <c r="G83">
-        <v>-5.424303532399859</v>
+        <v>-4.069668024276561</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.899599977670279</v>
       </c>
       <c r="E84">
-        <v>-19.05676262357806</v>
+        <v>-18.9171588268696</v>
       </c>
       <c r="F84">
-        <v>-2.520163005969513</v>
+        <v>-2.598559696970459</v>
       </c>
       <c r="G84">
-        <v>-4.70928528573699</v>
+        <v>-4.463709017633853</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.848124174237078</v>
       </c>
       <c r="E85">
-        <v>-19.16180057818598</v>
+        <v>-19.44032437202774</v>
       </c>
       <c r="F85">
-        <v>-2.80946700792763</v>
+        <v>-2.261634509760205</v>
       </c>
       <c r="G85">
-        <v>-4.79972607932434</v>
+        <v>-3.727645632977837</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.768474851338178</v>
       </c>
       <c r="E86">
-        <v>-20.85777749269463</v>
+        <v>-21.23015843881937</v>
       </c>
       <c r="F86">
-        <v>-2.774295356372166</v>
+        <v>-2.50689090344186</v>
       </c>
       <c r="G86">
-        <v>-5.484777267765726</v>
+        <v>-4.292709408893879</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.662529833468055</v>
       </c>
       <c r="E87">
-        <v>-22.05898692254725</v>
+        <v>-20.43888911851112</v>
       </c>
       <c r="F87">
-        <v>-3.197212535299633</v>
+        <v>-2.06149680340683</v>
       </c>
       <c r="G87">
-        <v>-4.736421827522396</v>
+        <v>-4.193542017265011</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.532652752598147</v>
       </c>
       <c r="E88">
-        <v>-23.25286928145545</v>
+        <v>-23.12948647864247</v>
       </c>
       <c r="F88">
-        <v>-2.850332028642535</v>
+        <v>-2.364607204867406</v>
       </c>
       <c r="G88">
-        <v>-4.865341091912694</v>
+        <v>-3.477951046223847</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.379720173744237</v>
       </c>
       <c r="E89">
-        <v>-23.69133424877413</v>
+        <v>-24.33752031882464</v>
       </c>
       <c r="F89">
-        <v>-2.814420644996371</v>
+        <v>-2.060356141493175</v>
       </c>
       <c r="G89">
-        <v>-4.704630658708775</v>
+        <v>-3.846136678919431</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.205847666780091</v>
       </c>
       <c r="E90">
-        <v>-25.59900826619336</v>
+        <v>-25.94896420903212</v>
       </c>
       <c r="F90">
-        <v>-2.610756578609279</v>
+        <v>-2.306815324643695</v>
       </c>
       <c r="G90">
-        <v>-4.666456758095439</v>
+        <v>-4.420953321994166</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.014405850186668</v>
       </c>
       <c r="E91">
-        <v>-27.45713172102066</v>
+        <v>-27.6237659790809</v>
       </c>
       <c r="F91">
-        <v>-2.805822191355312</v>
+        <v>-2.543112096496671</v>
       </c>
       <c r="G91">
-        <v>-4.855336623293018</v>
+        <v>-4.176108684455208</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>0.8062086934697235</v>
       </c>
       <c r="E92">
-        <v>-28.3271466758483</v>
+        <v>-29.28725109258453</v>
       </c>
       <c r="F92">
-        <v>-2.752541600007248</v>
+        <v>-2.876423945095914</v>
       </c>
       <c r="G92">
-        <v>-5.025882687294112</v>
+        <v>-3.509709109582075</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>0.5840298226370396</v>
       </c>
       <c r="E93">
-        <v>-30.60796468726256</v>
+        <v>-31.32750977200033</v>
       </c>
       <c r="F93">
-        <v>-2.544642091089642</v>
+        <v>-2.293032119428514</v>
       </c>
       <c r="G93">
-        <v>-5.534402345399402</v>
+        <v>-4.187993542941192</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.3528005814548417</v>
       </c>
       <c r="E94">
-        <v>-32.89674828445632</v>
+        <v>-33.49211581919275</v>
       </c>
       <c r="F94">
-        <v>-2.382680524861685</v>
+        <v>-2.292315581625093</v>
       </c>
       <c r="G94">
-        <v>-5.557625822357389</v>
+        <v>-3.950809507780108</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.114569621315836</v>
       </c>
       <c r="E95">
-        <v>-33.74487259593087</v>
+        <v>-35.29557380003646</v>
       </c>
       <c r="F95">
-        <v>-2.913839643945562</v>
+        <v>-2.013091154224241</v>
       </c>
       <c r="G95">
-        <v>-5.733700497409067</v>
+        <v>-5.348409275912068</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.1271053231783775</v>
       </c>
       <c r="E96">
-        <v>-36.14691106381946</v>
+        <v>-37.16923897765809</v>
       </c>
       <c r="F96">
-        <v>-2.677261227175634</v>
+        <v>-2.673074658321886</v>
       </c>
       <c r="G96">
-        <v>-5.662116571213406</v>
+        <v>-4.953381739984072</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.3648432879755017</v>
       </c>
       <c r="E97">
-        <v>-37.9151375168835</v>
+        <v>-38.68512980206671</v>
       </c>
       <c r="F97">
-        <v>-2.650319405766983</v>
+        <v>-2.382314386469648</v>
       </c>
       <c r="G97">
-        <v>-6.555533495896521</v>
+        <v>-4.993220845003662</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.5959283953649189</v>
       </c>
       <c r="E98">
-        <v>-40.35664163574893</v>
+        <v>-41.30410255305574</v>
       </c>
       <c r="F98">
-        <v>-2.47851434969156</v>
+        <v>-2.009693191137957</v>
       </c>
       <c r="G98">
-        <v>-6.473809368714072</v>
+        <v>-5.695860961895197</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.813864082558484</v>
       </c>
       <c r="E99">
-        <v>-42.69987334017391</v>
+        <v>-43.31835194200849</v>
       </c>
       <c r="F99">
-        <v>-2.462185571447576</v>
+        <v>-2.205433923317272</v>
       </c>
       <c r="G99">
-        <v>-6.78665261162966</v>
+        <v>-5.417189170035966</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.014152951230517</v>
       </c>
       <c r="E100">
-        <v>-44.49820055996693</v>
+        <v>-45.33722490292307</v>
       </c>
       <c r="F100">
-        <v>-2.527233121752408</v>
+        <v>-2.023727391676187</v>
       </c>
       <c r="G100">
-        <v>-7.072379176033078</v>
+        <v>-5.945035792999521</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.188579098990816</v>
       </c>
       <c r="E101">
-        <v>-47.1837350861577</v>
+        <v>-47.76205744472927</v>
       </c>
       <c r="F101">
-        <v>-2.505425521506308</v>
+        <v>-1.930749777651165</v>
       </c>
       <c r="G101">
-        <v>-7.560224477245619</v>
+        <v>-6.682420085325707</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.34038067072659</v>
       </c>
       <c r="E102">
-        <v>-49.25010268246473</v>
+        <v>-49.57541466975374</v>
       </c>
       <c r="F102">
-        <v>-2.312039009485749</v>
+        <v>-1.859832415930096</v>
       </c>
       <c r="G102">
-        <v>-7.549531415153774</v>
+        <v>-6.267943094354494</v>
       </c>
     </row>
   </sheetData>
